--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_sample_data_D2.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_sample_data_D2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -173,6 +173,15 @@
     <t xml:space="preserve">THU_BL_LOC</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THU_BL_UNK</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_151</t>
   </si>
   <si>
@@ -182,12 +191,15 @@
     <t xml:space="preserve">LC_154</t>
   </si>
   <si>
+    <t xml:space="preserve">LC_156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2bis</t>
+  </si>
+  <si>
     <t xml:space="preserve">LC_157</t>
   </si>
   <si>
-    <t xml:space="preserve">2bis</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_008</t>
   </si>
   <si>
@@ -299,10 +311,22 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAR_BL_LOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA</t>
   </si>
   <si>
     <t xml:space="preserve">MS_066</t>
@@ -1234,16 +1258,16 @@
         <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K9" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="N9" t="s">
         <v>32</v>
@@ -1266,7 +1290,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -1296,13 +1320,13 @@
         <v>28</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="L10" t="s">
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N10" t="s">
         <v>32</v>
@@ -1320,12 +1344,12 @@
         <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -1337,7 +1361,7 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -1352,16 +1376,16 @@
         <v>27</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="L11" t="s">
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N11" t="s">
         <v>32</v>
@@ -1379,15 +1403,15 @@
         <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>21</v>
@@ -1411,16 +1435,16 @@
         <v>27</v>
       </c>
       <c r="J12" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L12" t="s">
         <v>30</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="N12" t="s">
         <v>32</v>
@@ -1438,24 +1462,24 @@
         <v>34</v>
       </c>
       <c r="S12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -1470,51 +1494,51 @@
         <v>27</v>
       </c>
       <c r="J13" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O13" t="s">
         <v>26</v>
       </c>
       <c r="P13" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="s">
         <v>26</v>
       </c>
       <c r="R13" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" t="s">
         <v>59</v>
-      </c>
-      <c r="S13" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
         <v>24</v>
@@ -1532,36 +1556,36 @@
         <v>28</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" t="s">
+        <v>26</v>
+      </c>
+      <c r="P14" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S14" t="s">
         <v>61</v>
-      </c>
-      <c r="M14" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" t="s">
-        <v>26</v>
-      </c>
-      <c r="P14" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>26</v>
-      </c>
-      <c r="R14" t="s">
-        <v>59</v>
-      </c>
-      <c r="S14" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>36</v>
@@ -1570,7 +1594,7 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1591,13 +1615,13 @@
         <v>28</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N15" t="s">
         <v>26</v>
@@ -1606,30 +1630,30 @@
         <v>26</v>
       </c>
       <c r="P15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>26</v>
+      </c>
+      <c r="R15" t="s">
         <v>63</v>
       </c>
-      <c r="Q15" t="s">
-        <v>26</v>
-      </c>
-      <c r="R15" t="s">
-        <v>59</v>
-      </c>
       <c r="S15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1650,13 +1674,13 @@
         <v>28</v>
       </c>
       <c r="K16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N16" t="s">
         <v>26</v>
@@ -1665,30 +1689,30 @@
         <v>26</v>
       </c>
       <c r="P16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q16" t="s">
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="S16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1706,16 +1730,16 @@
         <v>27</v>
       </c>
       <c r="J17" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K17" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
         <v>26</v>
@@ -1724,30 +1748,30 @@
         <v>26</v>
       </c>
       <c r="P17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" t="s">
         <v>63</v>
       </c>
-      <c r="Q17" t="s">
-        <v>26</v>
-      </c>
-      <c r="R17" t="s">
-        <v>59</v>
-      </c>
       <c r="S17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1765,13 +1789,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
         <v>77</v>
@@ -1783,21 +1807,21 @@
         <v>26</v>
       </c>
       <c r="P18" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>26</v>
+      </c>
+      <c r="R18" t="s">
         <v>63</v>
       </c>
-      <c r="Q18" t="s">
-        <v>26</v>
-      </c>
-      <c r="R18" t="s">
-        <v>59</v>
-      </c>
       <c r="S18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -1806,10 +1830,10 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
         <v>24</v>
@@ -1827,13 +1851,13 @@
         <v>43</v>
       </c>
       <c r="K19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L19" t="s">
         <v>80</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>81</v>
-      </c>
-      <c r="M19" t="s">
-        <v>82</v>
       </c>
       <c r="N19" t="s">
         <v>26</v>
@@ -1848,15 +1872,15 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="S19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -1865,10 +1889,10 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E20" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
         <v>24</v>
@@ -1886,13 +1910,13 @@
         <v>43</v>
       </c>
       <c r="K20" t="s">
+        <v>79</v>
+      </c>
+      <c r="L20" t="s">
         <v>80</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>81</v>
-      </c>
-      <c r="M20" t="s">
-        <v>82</v>
       </c>
       <c r="N20" t="s">
         <v>26</v>
@@ -1907,15 +1931,15 @@
         <v>26</v>
       </c>
       <c r="R20" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="S20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -1924,7 +1948,7 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E21" t="s">
         <v>37</v>
@@ -1945,13 +1969,13 @@
         <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N21" t="s">
         <v>26</v>
@@ -1960,160 +1984,160 @@
         <v>26</v>
       </c>
       <c r="P21" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>26</v>
+      </c>
+      <c r="R21" t="s">
         <v>63</v>
       </c>
-      <c r="Q21" t="s">
-        <v>26</v>
-      </c>
-      <c r="R21" t="s">
-        <v>59</v>
-      </c>
       <c r="S21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22" t="s">
+        <v>85</v>
+      </c>
+      <c r="M22" t="s">
         <v>86</v>
       </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="N22" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" t="s">
+        <v>26</v>
+      </c>
+      <c r="P22" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>26</v>
+      </c>
+      <c r="R22" t="s">
+        <v>63</v>
+      </c>
+      <c r="S22" t="s">
         <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" t="s">
-        <v>27</v>
-      </c>
-      <c r="J22" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" t="s">
-        <v>69</v>
-      </c>
-      <c r="M22" t="s">
-        <v>70</v>
-      </c>
-      <c r="N22" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" t="s">
-        <v>26</v>
-      </c>
-      <c r="P22" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>26</v>
-      </c>
-      <c r="R22" t="s">
-        <v>34</v>
-      </c>
-      <c r="S22" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" t="s">
+        <v>85</v>
+      </c>
+      <c r="M23" t="s">
+        <v>89</v>
+      </c>
+      <c r="N23" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" t="s">
+        <v>26</v>
+      </c>
+      <c r="P23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" t="s">
+        <v>63</v>
+      </c>
+      <c r="S23" t="s">
         <v>88</v>
-      </c>
-      <c r="G23" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" t="s">
-        <v>27</v>
-      </c>
-      <c r="J23" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" t="s">
-        <v>69</v>
-      </c>
-      <c r="M23" t="s">
-        <v>70</v>
-      </c>
-      <c r="N23" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" t="s">
-        <v>26</v>
-      </c>
-      <c r="P23" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>26</v>
-      </c>
-      <c r="R23" t="s">
-        <v>34</v>
-      </c>
-      <c r="S23" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
         <v>91</v>
-      </c>
-      <c r="B24" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" t="s">
-        <v>87</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I24" t="s">
         <v>27</v>
@@ -2122,13 +2146,13 @@
         <v>28</v>
       </c>
       <c r="K24" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
@@ -2137,7 +2161,7 @@
         <v>26</v>
       </c>
       <c r="P24" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q24" t="s">
         <v>26</v>
@@ -2146,12 +2170,12 @@
         <v>34</v>
       </c>
       <c r="S24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
@@ -2160,19 +2184,19 @@
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I25" t="s">
         <v>27</v>
@@ -2181,13 +2205,13 @@
         <v>28</v>
       </c>
       <c r="K25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
         <v>26</v>
@@ -2196,7 +2220,7 @@
         <v>26</v>
       </c>
       <c r="P25" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q25" t="s">
         <v>26</v>
@@ -2205,12 +2229,12 @@
         <v>34</v>
       </c>
       <c r="S25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
@@ -2219,34 +2243,34 @@
         <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K26" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L26" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="M26" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N26" t="s">
         <v>26</v>
@@ -2255,7 +2279,7 @@
         <v>26</v>
       </c>
       <c r="P26" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q26" t="s">
         <v>26</v>
@@ -2264,12 +2288,12 @@
         <v>34</v>
       </c>
       <c r="S26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
         <v>36</v>
@@ -2278,34 +2302,34 @@
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I27" t="s">
         <v>27</v>
       </c>
       <c r="J27" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K27" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L27" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="M27" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
@@ -2314,7 +2338,7 @@
         <v>26</v>
       </c>
       <c r="P27" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q27" t="s">
         <v>26</v>
@@ -2323,12 +2347,12 @@
         <v>34</v>
       </c>
       <c r="S27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
@@ -2337,34 +2361,34 @@
         <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
       </c>
       <c r="H28" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s">
         <v>27</v>
       </c>
       <c r="J28" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K28" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L28" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M28" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="N28" t="s">
         <v>26</v>
@@ -2373,7 +2397,7 @@
         <v>26</v>
       </c>
       <c r="P28" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q28" t="s">
         <v>26</v>
@@ -2382,12 +2406,12 @@
         <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
@@ -2396,34 +2420,34 @@
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
         <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s">
         <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L29" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M29" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="N29" t="s">
         <v>26</v>
@@ -2432,7 +2456,7 @@
         <v>26</v>
       </c>
       <c r="P29" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q29" t="s">
         <v>26</v>
@@ -2441,12 +2465,12 @@
         <v>34</v>
       </c>
       <c r="S29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
@@ -2455,34 +2479,34 @@
         <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G30" t="s">
         <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I30" t="s">
         <v>27</v>
       </c>
       <c r="J30" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K30" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L30" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="M30" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="N30" t="s">
         <v>26</v>
@@ -2491,7 +2515,7 @@
         <v>26</v>
       </c>
       <c r="P30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q30" t="s">
         <v>26</v>
@@ -2500,12 +2524,12 @@
         <v>34</v>
       </c>
       <c r="S30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
         <v>36</v>
@@ -2514,34 +2538,34 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I31" t="s">
         <v>27</v>
       </c>
       <c r="J31" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L31" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="M31" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -2550,7 +2574,7 @@
         <v>26</v>
       </c>
       <c r="P31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q31" t="s">
         <v>26</v>
@@ -2559,12 +2583,12 @@
         <v>34</v>
       </c>
       <c r="S31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
@@ -2573,34 +2597,34 @@
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
         <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s">
         <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I32" t="s">
         <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K32" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
@@ -2609,7 +2633,7 @@
         <v>26</v>
       </c>
       <c r="P32" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q32" t="s">
         <v>26</v>
@@ -2618,12 +2642,12 @@
         <v>34</v>
       </c>
       <c r="S32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>36</v>
@@ -2632,34 +2656,34 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
         <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G33" t="s">
         <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K33" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
@@ -2668,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="P33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q33" t="s">
         <v>26</v>
@@ -2677,48 +2701,48 @@
         <v>34</v>
       </c>
       <c r="S33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I34" t="s">
         <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K34" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="L34" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="M34" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
@@ -2727,7 +2751,7 @@
         <v>26</v>
       </c>
       <c r="P34" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q34" t="s">
         <v>26</v>
@@ -2736,33 +2760,33 @@
         <v>34</v>
       </c>
       <c r="S34" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E35" t="s">
         <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s">
         <v>25</v>
       </c>
       <c r="H35" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="I35" t="s">
         <v>27</v>
@@ -2771,31 +2795,31 @@
         <v>28</v>
       </c>
       <c r="K35" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L35" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="N35" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="O35" t="s">
         <v>26</v>
       </c>
       <c r="P35" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>26</v>
+      </c>
+      <c r="R35" t="s">
+        <v>34</v>
+      </c>
+      <c r="S35" t="s">
         <v>107</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>26</v>
-      </c>
-      <c r="R35" t="s">
-        <v>34</v>
-      </c>
-      <c r="S35" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36">
@@ -2803,49 +2827,49 @@
         <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G36" t="s">
         <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="I36" t="s">
         <v>27</v>
       </c>
       <c r="J36" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L36" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M36" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="N36" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="O36" t="s">
         <v>26</v>
       </c>
       <c r="P36" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="Q36" t="s">
         <v>26</v>
@@ -2862,49 +2886,49 @@
         <v>109</v>
       </c>
       <c r="B37" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="E37" t="s">
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
         <v>25</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="I37" t="s">
         <v>27</v>
       </c>
       <c r="J37" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K37" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L37" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M37" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="N37" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O37" t="s">
         <v>26</v>
       </c>
       <c r="P37" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q37" t="s">
         <v>26</v>
@@ -2924,46 +2948,46 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
         <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s">
         <v>25</v>
       </c>
       <c r="H38" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="I38" t="s">
         <v>27</v>
       </c>
       <c r="J38" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L38" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="N38" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O38" t="s">
         <v>26</v>
       </c>
       <c r="P38" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q38" t="s">
         <v>26</v>
@@ -2986,13 +3010,13 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G39" t="s">
         <v>25</v>
@@ -3004,25 +3028,25 @@
         <v>27</v>
       </c>
       <c r="J39" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K39" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L39" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="M39" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N39" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
       </c>
       <c r="P39" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="Q39" t="s">
         <v>26</v>
@@ -3036,7 +3060,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s">
         <v>36</v>
@@ -3045,13 +3069,13 @@
         <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G40" t="s">
         <v>25</v>
@@ -3063,25 +3087,25 @@
         <v>27</v>
       </c>
       <c r="J40" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K40" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="L40" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="M40" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N40" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="O40" t="s">
         <v>26</v>
       </c>
       <c r="P40" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="Q40" t="s">
         <v>26</v>
@@ -3090,12 +3114,12 @@
         <v>34</v>
       </c>
       <c r="S40" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
         <v>20</v>
@@ -3110,7 +3134,7 @@
         <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
@@ -3122,16 +3146,16 @@
         <v>27</v>
       </c>
       <c r="J41" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K41" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="L41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M41" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="N41" t="s">
         <v>32</v>
@@ -3149,12 +3173,12 @@
         <v>34</v>
       </c>
       <c r="S41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
         <v>36</v>
@@ -3169,7 +3193,7 @@
         <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G42" t="s">
         <v>25</v>
@@ -3181,16 +3205,16 @@
         <v>27</v>
       </c>
       <c r="J42" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K42" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="L42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M42" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="N42" t="s">
         <v>32</v>
@@ -3208,12 +3232,12 @@
         <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
         <v>20</v>
@@ -3228,7 +3252,7 @@
         <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G43" t="s">
         <v>25</v>
@@ -3243,13 +3267,13 @@
         <v>43</v>
       </c>
       <c r="K43" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L43" t="s">
+        <v>80</v>
+      </c>
+      <c r="M43" t="s">
         <v>81</v>
-      </c>
-      <c r="M43" t="s">
-        <v>85</v>
       </c>
       <c r="N43" t="s">
         <v>32</v>
@@ -3258,7 +3282,7 @@
         <v>26</v>
       </c>
       <c r="P43" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q43" t="s">
         <v>26</v>
@@ -3267,12 +3291,12 @@
         <v>34</v>
       </c>
       <c r="S43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
         <v>36</v>
@@ -3287,7 +3311,7 @@
         <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G44" t="s">
         <v>25</v>
@@ -3302,13 +3326,13 @@
         <v>43</v>
       </c>
       <c r="K44" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L44" t="s">
+        <v>80</v>
+      </c>
+      <c r="M44" t="s">
         <v>81</v>
-      </c>
-      <c r="M44" t="s">
-        <v>85</v>
       </c>
       <c r="N44" t="s">
         <v>32</v>
@@ -3317,7 +3341,7 @@
         <v>26</v>
       </c>
       <c r="P44" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="Q44" t="s">
         <v>26</v>
@@ -3326,12 +3350,12 @@
         <v>34</v>
       </c>
       <c r="S44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
         <v>20</v>
@@ -3340,13 +3364,13 @@
         <v>47</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
@@ -3358,25 +3382,25 @@
         <v>27</v>
       </c>
       <c r="J45" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="L45" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M45" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="N45" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="O45" t="s">
         <v>26</v>
       </c>
       <c r="P45" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="Q45" t="s">
         <v>26</v>
@@ -3385,12 +3409,12 @@
         <v>34</v>
       </c>
       <c r="S45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B46" t="s">
         <v>36</v>
@@ -3399,13 +3423,13 @@
         <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
         <v>25</v>
@@ -3417,25 +3441,25 @@
         <v>27</v>
       </c>
       <c r="J46" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K46" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="L46" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M46" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="N46" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="O46" t="s">
         <v>26</v>
       </c>
       <c r="P46" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="Q46" t="s">
         <v>26</v>
@@ -3444,12 +3468,12 @@
         <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B47" t="s">
         <v>20</v>
@@ -3458,13 +3482,13 @@
         <v>47</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
         <v>25</v>
@@ -3476,25 +3500,25 @@
         <v>27</v>
       </c>
       <c r="J47" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="L47" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="M47" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="N47" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="O47" t="s">
         <v>26</v>
       </c>
       <c r="P47" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="Q47" t="s">
         <v>26</v>
@@ -3503,12 +3527,12 @@
         <v>34</v>
       </c>
       <c r="S47" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
         <v>36</v>
@@ -3517,13 +3541,13 @@
         <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G48" t="s">
         <v>25</v>
@@ -3535,25 +3559,25 @@
         <v>27</v>
       </c>
       <c r="J48" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="K48" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="L48" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="N48" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="O48" t="s">
         <v>26</v>
       </c>
       <c r="P48" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="Q48" t="s">
         <v>26</v>
@@ -3562,12 +3586,12 @@
         <v>34</v>
       </c>
       <c r="S48" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
         <v>20</v>
@@ -3576,13 +3600,13 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E49" t="s">
         <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G49" t="s">
         <v>25</v>
@@ -3597,22 +3621,22 @@
         <v>28</v>
       </c>
       <c r="K49" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L49" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M49" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N49" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
       </c>
       <c r="P49" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Q49" t="s">
         <v>26</v>
@@ -3621,12 +3645,12 @@
         <v>34</v>
       </c>
       <c r="S49" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
         <v>36</v>
@@ -3635,13 +3659,13 @@
         <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E50" t="s">
         <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G50" t="s">
         <v>25</v>
@@ -3656,22 +3680,22 @@
         <v>28</v>
       </c>
       <c r="K50" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L50" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M50" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N50" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O50" t="s">
         <v>26</v>
       </c>
       <c r="P50" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Q50" t="s">
         <v>26</v>
@@ -3680,12 +3704,12 @@
         <v>34</v>
       </c>
       <c r="S50" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B51" t="s">
         <v>20</v>
@@ -3694,13 +3718,13 @@
         <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G51" t="s">
         <v>25</v>
@@ -3715,22 +3739,22 @@
         <v>28</v>
       </c>
       <c r="K51" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L51" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M51" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N51" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O51" t="s">
         <v>26</v>
       </c>
       <c r="P51" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="Q51" t="s">
         <v>26</v>
@@ -3739,12 +3763,12 @@
         <v>34</v>
       </c>
       <c r="S51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B52" t="s">
         <v>36</v>
@@ -3753,13 +3777,13 @@
         <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E52" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F52" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G52" t="s">
         <v>25</v>
@@ -3774,22 +3798,22 @@
         <v>28</v>
       </c>
       <c r="K52" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="L52" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M52" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N52" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O52" t="s">
         <v>26</v>
       </c>
       <c r="P52" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="Q52" t="s">
         <v>26</v>
@@ -3798,12 +3822,12 @@
         <v>34</v>
       </c>
       <c r="S52" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B53" t="s">
         <v>20</v>
@@ -3812,13 +3836,13 @@
         <v>47</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E53" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F53" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -3830,26 +3854,26 @@
         <v>27</v>
       </c>
       <c r="J53" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K53" t="s">
+        <v>64</v>
+      </c>
+      <c r="L53" t="s">
+        <v>73</v>
+      </c>
+      <c r="M53" t="s">
+        <v>74</v>
+      </c>
+      <c r="N53" t="s">
         <v>114</v>
       </c>
-      <c r="L53" t="s">
-        <v>76</v>
-      </c>
-      <c r="M53" t="s">
+      <c r="O53" t="s">
+        <v>26</v>
+      </c>
+      <c r="P53" t="s">
         <v>115</v>
       </c>
-      <c r="N53" t="s">
-        <v>106</v>
-      </c>
-      <c r="O53" t="s">
-        <v>26</v>
-      </c>
-      <c r="P53" t="s">
-        <v>122</v>
-      </c>
       <c r="Q53" t="s">
         <v>26</v>
       </c>
@@ -3857,12 +3881,12 @@
         <v>34</v>
       </c>
       <c r="S53" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
         <v>36</v>
@@ -3871,13 +3895,13 @@
         <v>47</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G54" t="s">
         <v>25</v>
@@ -3889,26 +3913,26 @@
         <v>27</v>
       </c>
       <c r="J54" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K54" t="s">
+        <v>64</v>
+      </c>
+      <c r="L54" t="s">
+        <v>73</v>
+      </c>
+      <c r="M54" t="s">
+        <v>74</v>
+      </c>
+      <c r="N54" t="s">
         <v>114</v>
       </c>
-      <c r="L54" t="s">
-        <v>76</v>
-      </c>
-      <c r="M54" t="s">
+      <c r="O54" t="s">
+        <v>26</v>
+      </c>
+      <c r="P54" t="s">
         <v>115</v>
       </c>
-      <c r="N54" t="s">
-        <v>106</v>
-      </c>
-      <c r="O54" t="s">
-        <v>26</v>
-      </c>
-      <c r="P54" t="s">
-        <v>122</v>
-      </c>
       <c r="Q54" t="s">
         <v>26</v>
       </c>
@@ -3916,27 +3940,27 @@
         <v>34</v>
       </c>
       <c r="S54" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C55" t="s">
         <v>47</v>
       </c>
       <c r="D55" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F55" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G55" t="s">
         <v>25</v>
@@ -3948,25 +3972,25 @@
         <v>27</v>
       </c>
       <c r="J55" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L55" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M55" t="s">
         <v>77</v>
       </c>
       <c r="N55" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="O55" t="s">
         <v>26</v>
       </c>
       <c r="P55" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="Q55" t="s">
         <v>26</v>
@@ -3975,7 +3999,243 @@
         <v>34</v>
       </c>
       <c r="S55" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E56" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" t="s">
+        <v>113</v>
+      </c>
+      <c r="G56" t="s">
+        <v>25</v>
+      </c>
+      <c r="H56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" t="s">
+        <v>27</v>
+      </c>
+      <c r="J56" t="s">
+        <v>28</v>
+      </c>
+      <c r="K56" t="s">
+        <v>76</v>
+      </c>
+      <c r="L56" t="s">
+        <v>73</v>
+      </c>
+      <c r="M56" t="s">
+        <v>77</v>
+      </c>
+      <c r="N56" t="s">
+        <v>114</v>
+      </c>
+      <c r="O56" t="s">
+        <v>26</v>
+      </c>
+      <c r="P56" t="s">
         <v>130</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>26</v>
+      </c>
+      <c r="R56" t="s">
+        <v>34</v>
+      </c>
+      <c r="S56" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" t="s">
+        <v>113</v>
+      </c>
+      <c r="G57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" t="s">
+        <v>27</v>
+      </c>
+      <c r="J57" t="s">
+        <v>43</v>
+      </c>
+      <c r="K57" t="s">
+        <v>122</v>
+      </c>
+      <c r="L57" t="s">
+        <v>80</v>
+      </c>
+      <c r="M57" t="s">
+        <v>123</v>
+      </c>
+      <c r="N57" t="s">
+        <v>114</v>
+      </c>
+      <c r="O57" t="s">
+        <v>26</v>
+      </c>
+      <c r="P57" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>26</v>
+      </c>
+      <c r="R57" t="s">
+        <v>34</v>
+      </c>
+      <c r="S57" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D58" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" t="s">
+        <v>37</v>
+      </c>
+      <c r="F58" t="s">
+        <v>113</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" t="s">
+        <v>26</v>
+      </c>
+      <c r="I58" t="s">
+        <v>27</v>
+      </c>
+      <c r="J58" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" t="s">
+        <v>122</v>
+      </c>
+      <c r="L58" t="s">
+        <v>80</v>
+      </c>
+      <c r="M58" t="s">
+        <v>123</v>
+      </c>
+      <c r="N58" t="s">
+        <v>114</v>
+      </c>
+      <c r="O58" t="s">
+        <v>26</v>
+      </c>
+      <c r="P58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>26</v>
+      </c>
+      <c r="R58" t="s">
+        <v>34</v>
+      </c>
+      <c r="S58" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>138</v>
+      </c>
+      <c r="B59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C59" t="s">
+        <v>47</v>
+      </c>
+      <c r="D59" t="s">
+        <v>112</v>
+      </c>
+      <c r="E59" t="s">
+        <v>36</v>
+      </c>
+      <c r="F59" t="s">
+        <v>113</v>
+      </c>
+      <c r="G59" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" t="s">
+        <v>26</v>
+      </c>
+      <c r="I59" t="s">
+        <v>27</v>
+      </c>
+      <c r="J59" t="s">
+        <v>43</v>
+      </c>
+      <c r="K59" t="s">
+        <v>79</v>
+      </c>
+      <c r="L59" t="s">
+        <v>80</v>
+      </c>
+      <c r="M59" t="s">
+        <v>81</v>
+      </c>
+      <c r="N59" t="s">
+        <v>114</v>
+      </c>
+      <c r="O59" t="s">
+        <v>26</v>
+      </c>
+      <c r="P59" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>26</v>
+      </c>
+      <c r="R59" t="s">
+        <v>34</v>
+      </c>
+      <c r="S59" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
